--- a/data/daily/2026-09/2026-09-03.xlsx
+++ b/data/daily/2026-09/2026-09-03.xlsx
@@ -1170,14 +1170,114 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1192,17 +1292,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>2</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="361950" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1217,17 +1317,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1242,160 +1342,60 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>4</row>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>10</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>5</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>6</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>7</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>8</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>9</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>10</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -1425,52 +1425,152 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="990600" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>4</col>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1478,179 +1578,79 @@
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>10</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>11</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -2844,34 +2844,34 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>올인원 명품비타민 이뮨 멀티비타민 미네랄 7입+비타민젤리 마시는 액상 종합 비타민 수험생 직장인 부모님 건강 추석 선물</t>
+          <t>"올인원 명품비타민" 이뮨비타민 올인원 멀티비타민&amp;미네랄 프로 30병+쇼핑백증정</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>종근당</t>
+          <t>닥터블릿</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>23,800원</t>
+          <t>52,900원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/7948462</t>
+          <t>https://gift.kakao.com/product/10903147</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260902093524_a8f8c009362f4ec0affb7e118bf749cc.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260601193534_8d89165f65364cb0b3c77a98481c17d6.jpg</t>
         </is>
       </c>
     </row>
     <row r="12" ht="38" customHeight="1">
       <c r="B12" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -2879,34 +2879,34 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) + 파로저당단백칩 증정</t>
+          <t>[한끼통살] 단백질 든든형 닭가슴살 21일 식단관리+(증정)현미크리스피 닭가슴살 오리지널 1개</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>그레인온</t>
+          <t>한끼통살</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>24,900원</t>
+          <t>32,900원</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/13180362</t>
+          <t>https://gift.kakao.com/product/12860133</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260827152916_585042b9ed814333b774e55c37cb92ba.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260821134612_62bbe99621d6408d9e7e793b67d6e079.jpg</t>
         </is>
       </c>
     </row>
     <row r="13" ht="38" customHeight="1">
       <c r="B13" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -2914,27 +2914,27 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>[한끼통살] 단백질 든든형 닭가슴살 21일 식단관리+(증정)현미크리스피 닭가슴살 오리지널 1개</t>
+          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) + 파로저당단백칩 증정</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>한끼통살</t>
+          <t>그레인온</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>32,900원</t>
+          <t>24,900원</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/12860133</t>
+          <t>https://gift.kakao.com/product/13180362</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260821134612_62bbe99621d6408d9e7e793b67d6e079.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260827152916_585042b9ed814333b774e55c37cb92ba.jpg</t>
         </is>
       </c>
     </row>
@@ -3431,7 +3431,7 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>종근당</t>
+          <t>닥터블릿</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>올인원 명품비타민 이뮨 멀티비타민 미네랄 7입+비타민젤리 마시는 액상 종합 비타민 수험생 직장인 부모님 건강 추석 선물</t>
+          <t>"올인원 명품비타민" 이뮨비타민 올인원 멀티비타민&amp;미네랄 프로 30병+쇼핑백증정</t>
         </is>
       </c>
     </row>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>23,800원</t>
+          <t>52,900원</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
+          <t>한끼통살</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
           <t>그레인온</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>한끼통살</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -3802,12 +3802,12 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
+          <t>[한끼통살] 단백질 든든형 닭가슴살 21일 식단관리+(증정)현미크리스피 닭가슴살 오리지널 1개</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
           <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) + 파로저당단백칩 증정</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>[한끼통살] 단백질 든든형 닭가슴살 21일 식단관리+(증정)현미크리스피 닭가슴살 오리지널 1개</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
+          <t>32,900원</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
           <t>24,900원</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>32,900원</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -4062,34 +4062,34 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>홀베리 레몬 비타C 500 10개입</t>
+          <t>대웅제약 MSM 90정 30일분</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>홀베리</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=030086178&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000149&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260312/RhgSqjNOPs6aCmkpEpj2030086178_00_00RhgSqjNOPs6aCmkpEpj2.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/gVoECGdnaBQU8HtRPGFz600000149_00_00gVoECGdnaBQU8HtRPGFz.png</t>
         </is>
       </c>
     </row>
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -4097,12 +4097,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>동국제약 리포좀 마그마 스피드 30정</t>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910727&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000144&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20251111/69fT92p91uLANMODpyck610910727_00_0069fT92p91uLANMODpyck.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OqDM0kpIHoqFD3okk28W600000144_00_00OqDM0kpIHoqFD3okk28W.png</t>
         </is>
       </c>
     </row>
@@ -4132,34 +4132,34 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>종근당 데일리와이즈 초임계 알티지 오메가3 12캡슐 12일분</t>
+          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>종근당</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032306203&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000145&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260406/4kK0NmSBz1nQe0fBnnXY032306203_00_014kK0NmSBz1nQe0fBnnXY.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OHEcumxqCcJ047eosRhh600000145_00_00OHEcumxqCcJ047eosRhh.png</t>
         </is>
       </c>
     </row>
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -4167,7 +4167,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>대웅제약 바나바잎 추출물 30정 30일분</t>
+          <t>대웅제약 멀티비타민 미네랄 30정 30일분</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -4177,24 +4177,24 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000131&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000135&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/rCiQaBH4VQ1rKKr7rz83600000131_00_00rCiQaBH4VQ1rKKr7rz83.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/2ijoJLmHVT94XXIOZnda600000135_00_002ijoJLmHVT94XXIOZnda.png</t>
         </is>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>유한양행 프레쉬츄 생유산균 30정 30일분</t>
+          <t>자연관 이지슬로 엑스트라버진 올리브오일＆레몬 4병</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>유한양행</t>
+          <t>자연관</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -4217,19 +4217,19 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600651651&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032627034&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260325/Mz4AWbpywwVFSrdyow4Z600651651_00_00Mz4AWbpywwVFSrdyow4Z.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260810/jotmVom4KndGXbIlPcuj032627034_00_01jotmVom4KndGXbIlPcuj.jpg</t>
         </is>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -4237,34 +4237,34 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[우형재 PICK] 익스트림 모노크레아틴 플러스 120 g 40일분</t>
+          <t>대웅제약 마그네슘 30정 30일분</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=987253276&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000128&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260422/qm625V7JKEa8Iu7GrFAf987253276_00_01qm625V7JKEa8Iu7GrFAf.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/DZz3h5SxY2J2FqaEB9qZ600000128_00_00DZz3h5SxY2J2FqaEB9qZ.png</t>
         </is>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>비타민D</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[신혜선 PICK] 동국제약 프라임도스 비타민D3 4000IU 60정 60일분</t>
+          <t>[우형재 PICK] 익스트림 모노크레아틴 플러스 120 g 40일분</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -4287,19 +4287,19 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911095&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=987253276&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260814/OCdRZHWMgR1UGDUjFQp4610911095_00_01OCdRZHWMgR1UGDUjFQp4.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260422/qm625V7JKEa8Iu7GrFAf987253276_00_01qm625V7JKEa8Iu7GrFAf.jpg</t>
         </is>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -4307,27 +4307,27 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>대웅제약 비타민B 30정 30일분</t>
+          <t>[신혜선 PICK] 동국 마이팝 홍삼＆비타B</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>2,000원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000129&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911030&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/5QghHD5oyZssCfnGZbzA600000129_00_005QghHD5oyZssCfnGZbzA.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260623/xNJvNqGjAYp0B7f9QQ8M610911030_00_00xNJvNqGjAYp0B7f9QQ8M.jpg</t>
         </is>
       </c>
     </row>
@@ -4342,12 +4342,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>대웅제약 쏘팔메토 옥타코사놀 30캡슐 30일분</t>
+          <t>닥터블릿 푸응 7days 팻버닝 21캡슐</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>닥터블릿</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000139&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602085&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/Am2C7Da2wracg1TigkAF600000139_00_00Am2C7Da2wracg1TigkAF.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260624/m6tznB24o1VYvw4vwVs3613602085_00_00m6tznB24o1VYvw4vwVs3.jpg</t>
         </is>
       </c>
     </row>
@@ -4377,27 +4377,27 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>유한양행 프리바이오틱스 스틱 40포 20일분</t>
+          <t>대웅제약 철분 30정 30일분</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>유한양행</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600651647&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000133&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260325/3lk29dAMMktUiVesbwgQ600651647_00_003lk29dAMMktUiVesbwgQ.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260820/ahWGJ6KpupAlwxw7p3xm600000133_00_00ahWGJ6KpupAlwxw7p3xm.png</t>
         </is>
       </c>
     </row>
@@ -4517,37 +4517,37 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
+          <t>혈행</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>루테인/눈건강</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>멀티비타민/종합비타민</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>루테인/눈건강</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>마그네슘</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>비타민D</t>
-        </is>
-      </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
@@ -4569,52 +4569,52 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>홀베리</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>자연관</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>익스트림</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>동국제약</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>종근당</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>닥터블릿</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>대웅제약</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>유한양행</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>익스트림</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>동국제약</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>유한양행</t>
         </is>
       </c>
     </row>
@@ -4626,52 +4626,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>홀베리 레몬 비타C 500 10개입</t>
+          <t>대웅제약 MSM 90정 30일분</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>동국제약 리포좀 마그마 스피드 30정</t>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>종근당 데일리와이즈 초임계 알티지 오메가3 12캡슐 12일분</t>
+          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 바나바잎 추출물 30정 30일분</t>
+          <t>대웅제약 멀티비타민 미네랄 30정 30일분</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>유한양행 프레쉬츄 생유산균 30정 30일분</t>
+          <t>자연관 이지슬로 엑스트라버진 올리브오일＆레몬 4병</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
+          <t>대웅제약 마그네슘 30정 30일분</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
           <t>[우형재 PICK] 익스트림 모노크레아틴 플러스 120 g 40일분</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>[신혜선 PICK] 동국제약 프라임도스 비타민D3 4000IU 60정 60일분</t>
-        </is>
-      </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 비타민B 30정 30일분</t>
+          <t>[신혜선 PICK] 동국 마이팝 홍삼＆비타B</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 쏘팔메토 옥타코사놀 30캡슐 30일분</t>
+          <t>닥터블릿 푸응 7days 팻버닝 21캡슐</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>유한양행 프리바이오틱스 스틱 40포 20일분</t>
+          <t>대웅제약 철분 30정 30일분</t>
         </is>
       </c>
     </row>
@@ -4683,7 +4683,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>1,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -4693,42 +4693,42 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
           <t>2,000원</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
         <is>
           <t>3,000원</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>3,000원</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
         </is>
       </c>
     </row>
@@ -4867,7 +4867,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -4875,34 +4875,34 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>고려은단 비타민C1000 600정 (20개월분)</t>
+          <t>[1+1]알디콤 숙취해소제 4포입 3종 (플러스, 에이, 브이)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>고려은단</t>
+          <t>알디콤</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>42,900원</t>
+          <t>13,320원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000225938&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000245840&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022593803ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024584019ko.png?l=ko</t>
         </is>
       </c>
     </row>
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -4910,34 +4910,34 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[수면 효율증가]대원제약 대원헬스 꿀잠샷 20gX12포 (+2포+수면안대) (14일분)</t>
+          <t>[9월 올영픽] 고려은단 비타민C1000 이지+비타민D 120정 (+마이멜로디 파우치) (60일분)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>대원제약</t>
+          <t>고려은단</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>17,770원</t>
+          <t>10,600원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000247884&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000164736&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024788480ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0016/A00000016473622ko.png?l=ko</t>
         </is>
       </c>
     </row>
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -4945,34 +4945,34 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>판도라 브이트리티 7/14+1포 (7/15일분)</t>
+          <t>[웰니스 루틴] 온리추얼 슬리밍컷 다이어트/리셋 브이라인/글로우업 콜라겐 7포(+1포)/14포 (8/14일분)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>판도라</t>
+          <t>온리추얼</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>24,460원</t>
+          <t>12,940원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000227334&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000236701&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022733450ko.png?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0023/A00000023670137ko.png?l=ko</t>
         </is>
       </c>
     </row>
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -4980,34 +4980,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
+          <t>[스테디셀러 특가][감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>지노마스터</t>
+          <t>멜라메이트</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>27,400원</t>
+          <t>14,900원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000244929&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000223554&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024492930ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022355476ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -5015,34 +5015,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[1+1]알디콤 숙취해소제 4포입 3종 (플러스, 에이, 브이)</t>
+          <t>[파격특가] 콜레올로지 컷팅 젤리 레몬/키위/석류 10+2+2포 기획 외</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>알디콤</t>
+          <t>푸드올로지</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>13,320원</t>
+          <t>11,900원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000245840&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000183645&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024584019ko.png?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018364587ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -5050,27 +5050,27 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[피부건강] 글로우뮤즈 스킨 밸런스 파우더 레몬맛 14포 (14일분)</t>
+          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>글로우뮤즈</t>
+          <t>지노마스터</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>27,510원</t>
+          <t>27,400원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000246272&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000244929&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024627201ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024492943ko.png?l=ko</t>
         </is>
       </c>
     </row>
@@ -5085,34 +5085,34 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[9월 올영픽/산리오콜라보] CJ 이너비 브이 캔디 14포 (+마이멜로디 마그넷액자)</t>
+          <t>[스테디셀러 특가] 락토핏 골드 트리플 기획 (3개월분)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CJ이너비</t>
+          <t>락토핏</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>9,900원</t>
+          <t>17,900원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000264048&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000199062&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0026/A00000026404809ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0019/A00000019906245ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -5120,27 +5120,27 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>빌드 프리미엄 테프 효소 유산균 30포 (1개월분)</t>
+          <t>[9/3 하루특가] 오니스트 트리플콜라겐 오렌지 14일 (+스크런치 증정) / 케라그로우 망고 14일</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>빌드</t>
+          <t>오니스트</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>19,950원</t>
+          <t>29,400원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000235606&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000188804&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0023/A00000023560605ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018880441ko.png?l=ko</t>
         </is>
       </c>
     </row>
@@ -5155,27 +5155,27 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[스테디셀러 특가] 락토핏 골드 트리플 기획 (3개월분)</t>
+          <t>[9월 올영픽/품절대란] 닥터아돌 카테킨 아세로라 칼시페롤 C D 60정 (+시나모롤 틴케이스 키링)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>락토핏</t>
+          <t>닥터아돌</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>17,900원</t>
+          <t>24,900원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000199062&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000218073&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0019/A00000019906245ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0021/A00000021807373ko.png?l=ko</t>
         </is>
       </c>
     </row>
@@ -5190,27 +5190,27 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[스테디셀러 특가][감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
+          <t>[9/3 하루특가] 오니스트 트리플샤인 포도 14일</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>멜라메이트</t>
+          <t>오니스트</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>14,900원</t>
+          <t>27,900원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000223554&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000204000&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022355476ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020400044ko.png?l=ko</t>
         </is>
       </c>
     </row>
@@ -5325,42 +5325,42 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
           <t>비타민C/항산화</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>피부/미용</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
@@ -5382,52 +5382,52 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>알디콤</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>고려은단</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>대원제약</t>
-        </is>
-      </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>판도라</t>
+          <t>온리추얼</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
+          <t>멜라메이트</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>푸드올로지</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
           <t>지노마스터</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>알디콤</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>글로우뮤즈</t>
-        </is>
-      </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>CJ이너비</t>
+          <t>락토핏</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>빌드</t>
+          <t>오니스트</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>락토핏</t>
+          <t>닥터아돌</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>멜라메이트</t>
+          <t>오니스트</t>
         </is>
       </c>
     </row>
@@ -5439,52 +5439,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>고려은단 비타민C1000 600정 (20개월분)</t>
+          <t>[1+1]알디콤 숙취해소제 4포입 3종 (플러스, 에이, 브이)</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>[수면 효율증가]대원제약 대원헬스 꿀잠샷 20gX12포 (+2포+수면안대) (14일분)</t>
+          <t>[9월 올영픽] 고려은단 비타민C1000 이지+비타민D 120정 (+마이멜로디 파우치) (60일분)</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>판도라 브이트리티 7/14+1포 (7/15일분)</t>
+          <t>[웰니스 루틴] 온리추얼 슬리밍컷 다이어트/리셋 브이라인/글로우업 콜라겐 7포(+1포)/14포 (8/14일분)</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
+          <t>[스테디셀러 특가][감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>[파격특가] 콜레올로지 컷팅 젤리 레몬/키위/석류 10+2+2포 기획 외</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
           <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>[1+1]알디콤 숙취해소제 4포입 3종 (플러스, 에이, 브이)</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>[피부건강] 글로우뮤즈 스킨 밸런스 파우더 레몬맛 14포 (14일분)</t>
-        </is>
-      </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>[9월 올영픽/산리오콜라보] CJ 이너비 브이 캔디 14포 (+마이멜로디 마그넷액자)</t>
+          <t>[스테디셀러 특가] 락토핏 골드 트리플 기획 (3개월분)</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>빌드 프리미엄 테프 효소 유산균 30포 (1개월분)</t>
+          <t>[9/3 하루특가] 오니스트 트리플콜라겐 오렌지 14일 (+스크런치 증정) / 케라그로우 망고 14일</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>[스테디셀러 특가] 락토핏 골드 트리플 기획 (3개월분)</t>
+          <t>[9월 올영픽/품절대란] 닥터아돌 카테킨 아세로라 칼시페롤 C D 60정 (+시나모롤 틴케이스 키링)</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>[스테디셀러 특가][감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
+          <t>[9/3 하루특가] 오니스트 트리플샤인 포도 14일</t>
         </is>
       </c>
     </row>
@@ -5496,52 +5496,52 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>42,900원</t>
+          <t>13,320원</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>17,770원</t>
+          <t>10,600원</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>24,460원</t>
+          <t>12,940원</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
+          <t>14,900원</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>11,900원</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
           <t>27,400원</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>13,320원</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>27,510원</t>
-        </is>
-      </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>9,900원</t>
+          <t>17,900원</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>19,950원</t>
+          <t>29,400원</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>17,900원</t>
+          <t>24,900원</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>14,900원</t>
+          <t>27,900원</t>
         </is>
       </c>
     </row>
@@ -5629,7 +5629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5671,38 +5671,38 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C2" t="n">
-        <v>37.5</v>
+        <v>32.5</v>
       </c>
       <c r="D2" t="n">
         <v>4</v>
       </c>
       <c r="E2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2" t="n">
         <v>5</v>
-      </c>
-      <c r="F2" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="B3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C3" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="D3" t="n">
         <v>8</v>
       </c>
-      <c r="C3" t="n">
-        <v>20</v>
-      </c>
-      <c r="D3" t="n">
-        <v>6</v>
-      </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -5711,45 +5711,45 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4" t="n">
-        <v>20</v>
+        <v>22.5</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -5777,7 +5777,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -5790,10 +5790,10 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
         <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -5821,7 +5821,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -5831,19 +5831,19 @@
         <v>2.5</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>비타민D</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -5856,9 +5856,31 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
         <v>1</v>
       </c>
-      <c r="F10" t="n">
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>혈행</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
         <v>0</v>
       </c>
     </row>
